--- a/Assessment Questions/CDS/-BDF-117/HDFS AND MAP REDUCE/Key Terms_ Output Format, Partitioners,/Key Terms_ Output Format, Partitioners,.xlsx
+++ b/Assessment Questions/CDS/-BDF-117/HDFS AND MAP REDUCE/Key Terms_ Output Format, Partitioners,/Key Terms_ Output Format, Partitioners,.xlsx
@@ -1,165 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>Job_ID,Job_Name,Output_Format,Output_Format_Type,Compression,Compression_Codec,Partitioner_Type,Partition_Count,Partition_Key,Key_Class,Value_Class,Output_Files,File_Size_MB,Records_Per_File,Partition_Balance_Score,Skew_Detected,Total_Records,Unique_Keys,Spill_Count,Shuffle_Data_MB,Reduce_Tasks,Split_Size_MB,Block_Size_MB,Success_Status</t>
-  </si>
-  <si>
-    <t>JOB-001,WordCount,TextOutputFormat,Text,Yes,Snappy,HashPartitioner,8,word,Text,IntWritable,8,256,312500,0.92,No,2500000,1800000,12,3200,8,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-002,LogParser,SequenceFileOutputFormat,Binary,Yes,Gzip,HashPartitioner,16,log_level,Text,Text,16,512,612500,0.88,No,9800000,8200000,28,6500,16,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-003,SalesAgg,TextOutputFormat,Text,No,None,HashPartitioner,4,product_id,Text,IntWritable,4,32,80000,0.95,No,320000,320000,8,1800,4,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-004,ClickStream,AvroOutputFormat,Avro,Yes,Snappy,HashPartitioner,48,user_id,Text,AvroRecord,48,19200,656250,0.78,Yes,31500000,28500000,56,19200,48,128,128,Partial</t>
-  </si>
-  <si>
-    <t>JOB-005,UserSegment,ParquetOutputFormat,Parquet,Yes,Snappy,HashPartitioner,24,segment,Text,ParquetRecord,24,9600,400000,0.85,No,9600000,9600000,34,4800,24,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-006,FraudDetect,ORCOutputFormat,ORC,Yes,Zlib,RangePartitioner,8,account_id,Text,ORCRecord,8,1600,200000,0.72,Yes,1600000,1600000,78,12800,8,128,128,Partial</t>
-  </si>
-  <si>
-    <t>JOB-007,PageRank,SequenceFileOutputFormat,Binary,Yes,Snappy,TotalOrderPartitioner,128,page_id,IntWritable,FloatWritable,128,12800,93750,0.96,No,12000000,12000000,18,12800,128,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-008,ImageProcess,TextOutputFormat,Text,No,None,HashPartitioner,128,image_id,Text,Text,128,51200,19531,0.65,Yes,2500000,2100000,95,51200,128,64,128,Partial</t>
-  </si>
-  <si>
-    <t>JOB-009,ETL_Cleansing,AvroOutputFormat,Avro,Yes,Snappy,HashPartitioner,192,record_type,Text,AvroRecord,192,76800,80000,0.82,No,15360000,15360000,112,76800,192,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-010,SearchIndex,TextOutputFormat,Text,Yes,Gzip,HashPartitioner,256,keyword,Text,Text,256,25600,195312,0.91,No,50000000,50000000,24,25600,256,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-011,SensorData,SequenceFileOutputFormat,Binary,Yes,Snappy,HashPartitioner,8,sensor_id,IntWritable,DoubleWritable,8,3200,400000,0.94,No,3200000,3200000,14,2100,8,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-012,SocialNet,ParquetOutputFormat,Parquet,Yes,Zstd,HashPartitioner,128,user_id,Text,ParquetRecord,128,10800,84375,0.89,No,10800000,10800000,56,25600,128,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-013,Recommend,ORCOutputFormat,ORC,Yes,Snappy,HashPartitioner,64,product_id,Text,ORCRecord,64,25600,40000,0.93,No,2560000,2560000,32,19200,64,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-014,GenomeSeq,AvroOutputFormat,Avro,Yes,Zlib,RangePartitioner,256,chromosome,Text,AvroRecord,256,102400,40000,0.68,Yes,10240000,10240000,145,89600,256,128,128,Partial</t>
-  </si>
-  <si>
-    <t>JOB-015,LogAnalytics,ParquetOutputFormat,Parquet,Yes,Snappy,HashPartitioner,96,timestamp,LongWritable,ParquetRecord,96,38400,131250,0.86,No,12600000,12600000,68,38400,96,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-016,UserProfile,TextOutputFormat,Text,No,None,HashPartitioner,24,user_id,Text,Text,24,9600,400000,0.90,No,9600000,9600000,28,4800,24,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-017,ClickPrediction,SequenceFileOutputFormat,Binary,Yes,Snappy,HashPartitioner,32,click_id,Text,IntWritable,32,12800,400000,0.87,No,12800000,12800000,42,9600,32,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-018,DataValidation,TextOutputFormat,Text,Yes,Gzip,HashPartitioner,16,record_id,Text,Text,16,6400,400000,0.92,No,6400000,6400000,18,3200,16,128,128,Success</t>
-  </si>
-  <si>
-    <t>JOB-019,BackupOperation,AvroOutputFormat,Avro,Yes,Snappy,HashPartitioner,256,backup_key,Text,AvroRecord,256,204800,80000,0.71,Yes,20480000,20480000,112,102400,256,128,128,Partial</t>
-  </si>
-  <si>
-    <t>JOB-020,RealTimeAnalytics,ParquetOutputFormat,Parquet,Yes,Zstd,HashPartitioner,48,event_time,LongWritable,ParquetRecord,48,19200,400000,0.84,No,19200000,19200000,56,19200,48,128,128,Success</t>
-  </si>
-  <si>
-    <t>Q.No,Question,Key_Term,Analysis_Required,Expected_Answer,Key_Learning</t>
-  </si>
-  <si>
-    <t>1,"What is Output Format in MapReduce? List the different output formats from the dataset.","Output Format Definition","Analyze Output_Format column","TextOutputFormat (6 jobs), SequenceFileOutputFormat (4), AvroOutputFormat (4), ParquetOutputFormat (4), ORCOutputFormat (2)","Output formats determine how data is written to HDFS"</t>
-  </si>
-  <si>
-    <t>2,"What is TextOutputFormat? When should it be used? Analyze its characteristics from the dataset.","TextOutputFormat","Filter Output_Format='TextOutputFormat'","TextOutputFormat: Human-readable text. Used for WordCount, SalesAgg, SearchIndex, UserProfile, DataValidation. File sizes: 32-25,600 MB","Best for human-readable output and simple data exchange"</t>
-  </si>
-  <si>
-    <t>3,"What is SequenceFileOutputFormat? What are its advantages? Analyze from dataset.","SequenceFileOutputFormat","Filter Output_Format='SequenceFileOutputFormat'","Binary format with compression. Used for LogParser, PageRank, SensorData, ClickPrediction. Compression: Snappy, Gzip. Files: 3,200-12,800 MB","Efficient binary storage with compression; good for intermediate data"</t>
-  </si>
-  <si>
-    <t>4,"What is AvroOutputFormat? Why is schema evolution important? Analyze Avro jobs.","AvroOutputFormat","Filter Output_Format='AvroOutputFormat'","Avro: Schema-based serialization. Used for ClickStream, ETL, GenomeSeq, Backup. Compression: Snappy, Zlib. Files: 19,200-204,800 MB","Schema evolution allows adding/changing fields without breaking compatibility"</t>
-  </si>
-  <si>
-    <t>5,"What is ParquetOutputFormat? Why is it ideal for analytics? Analyze from dataset.","ParquetOutputFormat","Filter Output_Format='ParquetOutputFormat'","Columnar storage format. Used for UserSegment, SocialNet, LogAnalytics, RealTimeAnalytics. Compression: Snappy, Zstd. Files: 9,600-38,400 MB","Columnar format for analytics; high compression; predicate pushdown"</t>
-  </si>
-  <si>
-    <t>6,"What is ORCOutputFormat? How does it compare to Parquet? Analyze ORC jobs.","ORCOutputFormat","Filter Output_Format='ORCOutputFormat'","Optimized Row Columnar format. Used for FraudDetect, Recommend. Compression: Zlib, Snappy. Files: 1,600-25,600 MB","Similar to Parquet; optimized for Hive; better compression"</t>
-  </si>
-  <si>
-    <t>7,"What is compression in MapReduce? Analyze compression usage and codecs.","Compression","Analyze Compression, Compression_Codec","Compression used: 85% of jobs (17/20). Codecs: Snappy (60%), Gzip (20%), Zlib (10%), Zstd (10%), None (15%)","Compression reduces storage and network I/O significantly"</t>
-  </si>
-  <si>
-    <t>8,"What is Snappy compression? Compare compression codecs from the dataset.","Compression Codecs","Compare Compression_Codec metrics","Snappy: 60% usage, fast, moderate compression; Gzip: 20%, slower, high compression; Zlib: 10%, good balance; Zstd: 10%, high compression ratio","Choose codec based on speed vs compression ratio requirements"</t>
-  </si>
-  <si>
-    <t>9,"What is a Partitioner in MapReduce? Explain its role using the dataset.","Partitioner Definition","Analyze Partitioner_Type, Partition_Count","Partitioner determines which reducer processes each key. Types: HashPartitioner (85%), RangePartitioner (10%), TotalOrderPartitioner (5%)","Partitioner controls data distribution across reducers"</t>
-  </si>
-  <si>
-    <t>10,"What is HashPartitioner? How does it work? Analyze its usage and balance.","HashPartitioner","Filter Partitioner_Type='HashPartitioner'","Default partitioner. Uses hash(key) % partitions. Balance score: 0.78-0.95. Best balance: 0.95 (SalesAgg); Skewed: 0.65 (ImageProcess)","HashPartitioner provides good distribution for random keys"</t>
-  </si>
-  <si>
-    <t>11,"What is RangePartitioner? When should it be used? Analyze RangePartitioner jobs.","RangePartitioner","Filter Partitioner_Type='RangePartitioner'","RangePartitioner: Keys sorted into ranges. Used for FraudDetect, GenomeSeq. Balance score: 0.68-0.72. Skew detected in both","Best for keys with natural ordering; requires sampling for range boundaries"</t>
-  </si>
-  <si>
-    <t>12,"What is TotalOrderPartitioner? Analyze its characteristics from the dataset.","TotalOrderPartitioner","Filter Partitioner_Type='TotalOrderPartitioner'","TotalOrderPartitioner: Maintains global sort order. Used for PageRank. Balance score: 0.96 (excellent balance)","Ensures globally sorted output; good for indexed data"</t>
-  </si>
-  <si>
-    <t>13,"What is partition count? How does it affect parallelism? Analyze partition distribution.","Partition Count","Analyze Partition_Count, Reduce_Tasks","Partition count equals reduce tasks (4-256). More partitions = more parallelism but more files. Optimal: 1 per 100 MB output","Partition count determines number of output files and parallelism"</t>
-  </si>
-  <si>
-    <t>14,"What is partition balance score? Calculate average balance and identify skew.","Partition Balance","Analyze Partition_Balance_Score, Skew_Detected","Average balance: 0.86. Balanced (&gt;0.9): 55% jobs; Moderate (0.8-0.9): 30%; Skewed (&lt;0.8): 15%. Skew detected in 6 jobs","Balance score measures evenness of data distribution across partitions"</t>
-  </si>
-  <si>
-    <t>15,"What causes partition skew? Identify skewed jobs and analyze patterns.","Data Skew","Filter Skew_Detected='Yes'","Skewed jobs: ClickStream (0.78), FraudDetect (0.72), ImageProcess (0.65), GenomeSeq (0.68), Backup (0.71). Common in high cardinality keys","Skew occurs when keys are not uniformly distributed; custom partitioner needed"</t>
-  </si>
-  <si>
-    <t>16,"What is the relationship between partition count and output files? Analyze from dataset.","Output Files","Analyze Partition_Count vs Output_Files","Output_Files = Partition_Count for all jobs. Each reducer writes one output file. More reducers = more files","Number of output files equals number of reduce tasks"</t>
-  </si>
-  <si>
-    <t>17,"What is records per file? How does file size vary with partition count?","File Distribution","Calculate Records_Per_File, File_Size_MB","Small partitions (4): 80K records/file, 32 MB; Large partitions (256): 19K-195K records/file, 25,600-204,800 MB","Records per file varies inversely with partition count"</t>
-  </si>
-  <si>
-    <t>18,"What is the difference between key class and value class? Analyze data types.","Key-Value Classes","Analyze Key_Class, Value_Class","Keys: Text (55%), IntWritable (15%), LongWritable (10%), others; Values: IntWritable (25%), Text (25%), Avro/Parquet/ORC (50%)","Data types affect serialization performance and storage efficiency"</t>
-  </si>
-  <si>
-    <t>19,"What are the performance characteristics of different output formats? Compare compression and file sizes.","Format Performance","Group by Output_Format; average File_Size_MB","Text: 9,200 MB (largest), SequenceFile: 5,700 MB, Avro: 47,800 MB (largest files), Parquet: 19,200 MB, ORC: 13,600 MB","Columnar formats (Parquet/ORC) offer better compression than row-based formats"</t>
-  </si>
-  <si>
-    <t>20,"Create an output format and partitioner recommendation guide based on job characteristics.","Best Practices","Map job types to optimal format and partitioner","Analytics: Parquet/ORC + HashPartitioner; ETL: Avro + HashPartitioner; Indexing: SequenceFile + TotalOrderPartitioner; Simple output: TextOutputFormat","Choose format based on use case; partitioner based on key distribution"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -169,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -393,235 +316,913 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Job_ID,Job_Name,Output_Format,Output_Format_Type,Compression,Compression_Codec,Partitioner_Type,Partition_Count,Partition_Key,Key_Class,Value_Class,Output_Files,File_Size_MB,Records_Per_File,Partition_Balance_Score,Skew_Detected,Total_Records,Unique_Keys,Spill_Count,Shuffle_Data_MB,Reduce_Tasks,Split_Size_MB,Block_Size_MB,Success_Status</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>JOB-001,WordCount,TextOutputFormat,Text,Yes,Snappy,HashPartitioner,8,word,Text,IntWritable,8,256,312500,0.92,No,2500000,1800000,12,3200,8,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>JOB-002,LogParser,SequenceFileOutputFormat,Binary,Yes,Gzip,HashPartitioner,16,log_level,Text,Text,16,512,612500,0.88,No,9800000,8200000,28,6500,16,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>JOB-003,SalesAgg,TextOutputFormat,Text,No,None,HashPartitioner,4,product_id,Text,IntWritable,4,32,80000,0.95,No,320000,320000,8,1800,4,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>JOB-004,ClickStream,AvroOutputFormat,Avro,Yes,Snappy,HashPartitioner,48,user_id,Text,AvroRecord,48,19200,656250,0.78,Yes,31500000,28500000,56,19200,48,128,128,Partial</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>JOB-005,UserSegment,ParquetOutputFormat,Parquet,Yes,Snappy,HashPartitioner,24,segment,Text,ParquetRecord,24,9600,400000,0.85,No,9600000,9600000,34,4800,24,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>JOB-006,FraudDetect,ORCOutputFormat,ORC,Yes,Zlib,RangePartitioner,8,account_id,Text,ORCRecord,8,1600,200000,0.72,Yes,1600000,1600000,78,12800,8,128,128,Partial</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>JOB-007,PageRank,SequenceFileOutputFormat,Binary,Yes,Snappy,TotalOrderPartitioner,128,page_id,IntWritable,FloatWritable,128,12800,93750,0.96,No,12000000,12000000,18,12800,128,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>JOB-008,ImageProcess,TextOutputFormat,Text,No,None,HashPartitioner,128,image_id,Text,Text,128,51200,19531,0.65,Yes,2500000,2100000,95,51200,128,64,128,Partial</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>JOB-009,ETL_Cleansing,AvroOutputFormat,Avro,Yes,Snappy,HashPartitioner,192,record_type,Text,AvroRecord,192,76800,80000,0.82,No,15360000,15360000,112,76800,192,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>JOB-010,SearchIndex,TextOutputFormat,Text,Yes,Gzip,HashPartitioner,256,keyword,Text,Text,256,25600,195312,0.91,No,50000000,50000000,24,25600,256,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>JOB-011,SensorData,SequenceFileOutputFormat,Binary,Yes,Snappy,HashPartitioner,8,sensor_id,IntWritable,DoubleWritable,8,3200,400000,0.94,No,3200000,3200000,14,2100,8,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>JOB-012,SocialNet,ParquetOutputFormat,Parquet,Yes,Zstd,HashPartitioner,128,user_id,Text,ParquetRecord,128,10800,84375,0.89,No,10800000,10800000,56,25600,128,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>JOB-013,Recommend,ORCOutputFormat,ORC,Yes,Snappy,HashPartitioner,64,product_id,Text,ORCRecord,64,25600,40000,0.93,No,2560000,2560000,32,19200,64,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>JOB-014,GenomeSeq,AvroOutputFormat,Avro,Yes,Zlib,RangePartitioner,256,chromosome,Text,AvroRecord,256,102400,40000,0.68,Yes,10240000,10240000,145,89600,256,128,128,Partial</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>JOB-015,LogAnalytics,ParquetOutputFormat,Parquet,Yes,Snappy,HashPartitioner,96,timestamp,LongWritable,ParquetRecord,96,38400,131250,0.86,No,12600000,12600000,68,38400,96,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>JOB-016,UserProfile,TextOutputFormat,Text,No,None,HashPartitioner,24,user_id,Text,Text,24,9600,400000,0.90,No,9600000,9600000,28,4800,24,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>JOB-017,ClickPrediction,SequenceFileOutputFormat,Binary,Yes,Snappy,HashPartitioner,32,click_id,Text,IntWritable,32,12800,400000,0.87,No,12800000,12800000,42,9600,32,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>JOB-018,DataValidation,TextOutputFormat,Text,Yes,Gzip,HashPartitioner,16,record_id,Text,Text,16,6400,400000,0.92,No,6400000,6400000,18,3200,16,128,128,Success</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>JOB-019,BackupOperation,AvroOutputFormat,Avro,Yes,Snappy,HashPartitioner,256,backup_key,Text,AvroRecord,256,204800,80000,0.71,Yes,20480000,20480000,112,102400,256,128,128,Partial</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>JOB-020,RealTimeAnalytics,ParquetOutputFormat,Parquet,Yes,Zstd,HashPartitioner,48,event_time,LongWritable,ParquetRecord,48,19200,400000,0.84,No,19200000,19200000,56,19200,48,128,128,Success</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is Output Format in MapReduce? List the different output formats from the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Output_Format column | TextOutputFormat (6 jobs), SequenceFileOutputFormat (4), AvroOutputFormat (4), ParquetOutputFormat (4), ORCOutputFormat (2)</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Output formats determine how data is written to HDFS</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What is TextOutputFormat? When should it be used? Analyze its characteristics from the dataset.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Filter Output_Format='TextOutputFormat' | TextOutputFormat: Human-readable text. Used for WordCount, SalesAgg, SearchIndex, UserProfile, DataValidation. File sizes: 32-25,600 MB</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Best for human-readable output and simple data exchange</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is SequenceFileOutputFormat? What are its advantages? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Filter Output_Format='SequenceFileOutputFormat' | Binary format with compression. Used for LogParser, PageRank, SensorData, ClickPrediction. Compression: Snappy, Gzip. Files: 3,200-12,800 MB</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Efficient binary storage with compression; good for intermediate data</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>What is AvroOutputFormat? Why is schema evolution important? Analyze Avro jobs.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Filter Output_Format='AvroOutputFormat' | Avro: Schema-based serialization. Used for ClickStream, ETL, GenomeSeq, Backup. Compression: Snappy, Zlib. Files: 19,200-204,800 MB</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Schema evolution allows adding/changing fields without breaking compatibility</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is ParquetOutputFormat? Why is it ideal for analytics? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Filter Output_Format='ParquetOutputFormat' | Columnar storage format. Used for UserSegment, SocialNet, LogAnalytics, RealTimeAnalytics. Compression: Snappy, Zstd. Files: 9,600-38,400 MB</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Columnar format for analytics; high compression; predicate pushdown</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>What is ORCOutputFormat? How does it compare to Parquet? Analyze ORC jobs.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Filter Output_Format='ORCOutputFormat' | Optimized Row Columnar format. Used for FraudDetect, Recommend. Compression: Zlib, Snappy. Files: 1,600-25,600 MB</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Similar to Parquet; optimized for Hive; better compression</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What is compression in MapReduce? Analyze compression usage and codecs.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Compression, Compression_Codec | Compression used: 85% of jobs (17/20). Codecs: Snappy (60%), Gzip (20%), Zlib (10%), Zstd (10%), None (15%)</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Compression reduces storage and network I/O significantly</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>What is Snappy compression? Compare compression codecs from the dataset.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Compare Compression_Codec metrics | Snappy: 60% usage, fast, moderate compression; Gzip: 20%, slower, high compression; Zlib: 10%, good balance; Zstd: 10%, high compression ratio</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Choose codec based on speed vs compression ratio requirements</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is a Partitioner in MapReduce? Explain its role using the dataset.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Partitioner_Type, Partition_Count | Partitioner determines which reducer processes each key. Types: HashPartitioner (85%), RangePartitioner (10%), TotalOrderPartitioner (5%)</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Partitioner controls data distribution across reducers</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What is HashPartitioner? How does it work? Analyze its usage and balance.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Filter Partitioner_Type='HashPartitioner' | Default partitioner. Uses hash(key) % partitions. Balance score: 0.78-0.95. Best balance: 0.95 (SalesAgg); Skewed: 0.65 (ImageProcess)</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>HashPartitioner provides good distribution for random keys</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What is RangePartitioner? When should it be used? Analyze RangePartitioner jobs.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Filter Partitioner_Type='RangePartitioner' | RangePartitioner: Keys sorted into ranges. Used for FraudDetect, GenomeSeq. Balance score: 0.68-0.72. Skew detected in both</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Best for keys with natural ordering; requires sampling for range boundaries</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What is TotalOrderPartitioner? Analyze its characteristics from the dataset.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Filter Partitioner_Type='TotalOrderPartitioner' | TotalOrderPartitioner: Maintains global sort order. Used for PageRank. Balance score: 0.96 (excellent balance)</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Ensures globally sorted output; good for indexed data</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What is partition count? How does it affect parallelism? Analyze partition distribution.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Partition_Count, Reduce_Tasks | Partition count equals reduce tasks (4-256). More partitions = more parallelism but more files. Optimal: 1 per 100 MB output</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Partition count determines number of output files and parallelism</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>What is partition balance score? Calculate average balance and identify skew.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Partition_Balance_Score, Skew_Detected | Average balance: 0.86. Balanced (&gt;0.9): 55% jobs; Moderate (0.8-0.9): 30%; Skewed (&lt;0.8): 15%. Skew detected in 6 jobs</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Balance score measures evenness of data distribution across partitions</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What causes partition skew? Identify skewed jobs and analyze patterns.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Filter Skew_Detected='Yes' | Skewed jobs: ClickStream (0.78), FraudDetect (0.72), ImageProcess (0.65), GenomeSeq (0.68), Backup (0.71). Common in high cardinality keys</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Skew occurs when keys are not uniformly distributed; custom partitioner needed</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What is the relationship between partition count and output files? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Partition_Count vs Output_Files | Output_Files = Partition_Count for all jobs. Each reducer writes one output file. More reducers = more files</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Number of output files equals number of reduce tasks</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What is records per file? How does file size vary with partition count?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Calculate Records_Per_File, File_Size_MB | Small partitions (4): 80K records/file, 32 MB; Large partitions (256): 19K-195K records/file, 25,600-204,800 MB</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Records per file varies inversely with partition count</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between key class and value class? Analyze data types.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Key_Class, Value_Class | Keys: Text (55%), IntWritable (15%), LongWritable (10%), others; Values: IntWritable (25%), Text (25%), Avro/Parquet/ORC (50%)</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Data types affect serialization performance and storage efficiency</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>What are the performance characteristics of different output formats? Compare compression and file sizes.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Group by Output_Format; average File_Size_MB | Text: 9,200 MB (largest), SequenceFile: 5,700 MB, Avro: 47,800 MB (largest files), Parquet: 19,200 MB, ORC: 13,600 MB</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Columnar formats (Parquet/ORC) offer better compression than row-based formats</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Key Terms_ Output Format, Partitioners,</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create an output format and partitioner recommendation guide based on job characteristics.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Map job types to optimal format and partitioner | Analytics: Parquet/ORC + HashPartitioner; ETL: Avro + HashPartitioner; Indexing: SequenceFile + TotalOrderPartitioner; Simple output: TextOutputFormat</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Choose format based on use case; partitioner based on key distribution</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>